--- a/output/yearly_population_iteration_73_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_73_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6009</v>
+        <v>5384</v>
       </c>
       <c r="C2" t="n">
-        <v>10153</v>
+        <v>4358</v>
       </c>
       <c r="D2" t="n">
-        <v>38808</v>
+        <v>21742</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4193</v>
+        <v>3031</v>
       </c>
       <c r="C3" t="n">
-        <v>7753</v>
+        <v>4501</v>
       </c>
       <c r="D3" t="n">
-        <v>18449</v>
+        <v>16426</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2782</v>
+        <v>2558</v>
       </c>
       <c r="C4" t="n">
-        <v>7118</v>
+        <v>5243</v>
       </c>
       <c r="D4" t="n">
-        <v>8453</v>
+        <v>9008</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1765</v>
+        <v>1601</v>
       </c>
       <c r="C5" t="n">
-        <v>4791</v>
+        <v>4592</v>
       </c>
       <c r="D5" t="n">
-        <v>3223</v>
+        <v>3320</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1070</v>
+        <v>906</v>
       </c>
       <c r="C6" t="n">
-        <v>3032</v>
+        <v>2826</v>
       </c>
       <c r="D6" t="n">
-        <v>1283</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>530</v>
+        <v>444</v>
       </c>
       <c r="C7" t="n">
-        <v>1716</v>
+        <v>1343</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>675</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>783</v>
+        <v>558</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>340</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1052,7 +1052,7 @@
         <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7312</v>
+        <v>5353</v>
       </c>
       <c r="C2" t="n">
-        <v>7663</v>
+        <v>14888</v>
       </c>
       <c r="D2" t="n">
-        <v>41049</v>
+        <v>31413</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4066</v>
+        <v>3306</v>
       </c>
       <c r="C3" t="n">
-        <v>7769</v>
+        <v>3895</v>
       </c>
       <c r="D3" t="n">
-        <v>19844</v>
+        <v>16045</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2874</v>
+        <v>2370</v>
       </c>
       <c r="C4" t="n">
-        <v>7194</v>
+        <v>4770</v>
       </c>
       <c r="D4" t="n">
-        <v>9650</v>
+        <v>9858</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1935</v>
+        <v>1781</v>
       </c>
       <c r="C5" t="n">
-        <v>5741</v>
+        <v>4758</v>
       </c>
       <c r="D5" t="n">
-        <v>3928</v>
+        <v>4147</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1252</v>
+        <v>1110</v>
       </c>
       <c r="C6" t="n">
-        <v>3733</v>
+        <v>3611</v>
       </c>
       <c r="D6" t="n">
-        <v>1532</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>674</v>
+        <v>576</v>
       </c>
       <c r="C7" t="n">
-        <v>2282</v>
+        <v>1997</v>
       </c>
       <c r="D7" t="n">
-        <v>746</v>
+        <v>765</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>292</v>
+        <v>252</v>
       </c>
       <c r="C8" t="n">
-        <v>1159</v>
+        <v>903</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>517</v>
+        <v>390</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1206,7 +1206,7 @@
         <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
         <v>248</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
         <v>179</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7057</v>
+        <v>7346</v>
       </c>
       <c r="C2" t="n">
-        <v>9814</v>
+        <v>16970</v>
       </c>
       <c r="D2" t="n">
-        <v>34962</v>
+        <v>42535</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4322</v>
+        <v>3388</v>
       </c>
       <c r="C3" t="n">
-        <v>6887</v>
+        <v>7497</v>
       </c>
       <c r="D3" t="n">
-        <v>21118</v>
+        <v>16959</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2838</v>
+        <v>2370</v>
       </c>
       <c r="C4" t="n">
-        <v>7212</v>
+        <v>4238</v>
       </c>
       <c r="D4" t="n">
-        <v>10824</v>
+        <v>10508</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2037</v>
+        <v>1800</v>
       </c>
       <c r="C5" t="n">
-        <v>6152</v>
+        <v>4618</v>
       </c>
       <c r="D5" t="n">
-        <v>4539</v>
+        <v>4803</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1382</v>
+        <v>1259</v>
       </c>
       <c r="C6" t="n">
-        <v>4454</v>
+        <v>4062</v>
       </c>
       <c r="D6" t="n">
-        <v>1834</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>805</v>
+        <v>710</v>
       </c>
       <c r="C7" t="n">
-        <v>2849</v>
+        <v>2640</v>
       </c>
       <c r="D7" t="n">
-        <v>831</v>
+        <v>860</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="C8" t="n">
-        <v>1565</v>
+        <v>1342</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>499</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>744</v>
+        <v>582</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>347</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6647</v>
+        <v>6606</v>
       </c>
       <c r="C2" t="n">
-        <v>6830</v>
+        <v>11539</v>
       </c>
       <c r="D2" t="n">
-        <v>28983</v>
+        <v>34679</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5106</v>
+        <v>4184</v>
       </c>
       <c r="C3" t="n">
-        <v>10747</v>
+        <v>10942</v>
       </c>
       <c r="D3" t="n">
-        <v>22584</v>
+        <v>18756</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1882</v>
+        <v>1663</v>
       </c>
       <c r="C4" t="n">
-        <v>9713</v>
+        <v>6792</v>
       </c>
       <c r="D4" t="n">
-        <v>10203</v>
+        <v>10280</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1276</v>
+        <v>1163</v>
       </c>
       <c r="C5" t="n">
-        <v>4364</v>
+        <v>3980</v>
       </c>
       <c r="D5" t="n">
-        <v>3017</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>743</v>
+        <v>656</v>
       </c>
       <c r="C6" t="n">
-        <v>2792</v>
+        <v>2587</v>
       </c>
       <c r="D6" t="n">
-        <v>814</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>358</v>
+        <v>313</v>
       </c>
       <c r="C7" t="n">
-        <v>1533</v>
+        <v>1315</v>
       </c>
       <c r="D7" t="n">
-        <v>472</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>729</v>
+        <v>570</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>340</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4268</v>
+        <v>3933</v>
       </c>
       <c r="C2" t="n">
-        <v>3259</v>
+        <v>5509</v>
       </c>
       <c r="D2" t="n">
-        <v>21313</v>
+        <v>23730</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4988</v>
+        <v>4483</v>
       </c>
       <c r="C3" t="n">
-        <v>8200</v>
+        <v>10157</v>
       </c>
       <c r="D3" t="n">
-        <v>22370</v>
+        <v>19841</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2654</v>
+        <v>2310</v>
       </c>
       <c r="C4" t="n">
-        <v>10350</v>
+        <v>8863</v>
       </c>
       <c r="D4" t="n">
-        <v>11871</v>
+        <v>11466</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1422</v>
+        <v>1278</v>
       </c>
       <c r="C5" t="n">
-        <v>6546</v>
+        <v>5249</v>
       </c>
       <c r="D5" t="n">
-        <v>3811</v>
+        <v>4027</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>867</v>
+        <v>788</v>
       </c>
       <c r="C6" t="n">
-        <v>3491</v>
+        <v>3200</v>
       </c>
       <c r="D6" t="n">
-        <v>1018</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>335</v>
+        <v>295</v>
       </c>
       <c r="C7" t="n">
-        <v>1973</v>
+        <v>1779</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>970</v>
+        <v>774</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>373</v>
+        <v>331</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5813</v>
+        <v>3498</v>
       </c>
       <c r="C2" t="n">
-        <v>7122</v>
+        <v>4293</v>
       </c>
       <c r="D2" t="n">
-        <v>31344</v>
+        <v>19021</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3949</v>
+        <v>3568</v>
       </c>
       <c r="C3" t="n">
-        <v>5318</v>
+        <v>7069</v>
       </c>
       <c r="D3" t="n">
-        <v>20722</v>
+        <v>19226</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3124</v>
+        <v>2804</v>
       </c>
       <c r="C4" t="n">
-        <v>9123</v>
+        <v>9312</v>
       </c>
       <c r="D4" t="n">
-        <v>13223</v>
+        <v>12484</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1703</v>
+        <v>1523</v>
       </c>
       <c r="C5" t="n">
-        <v>8126</v>
+        <v>6839</v>
       </c>
       <c r="D5" t="n">
-        <v>4933</v>
+        <v>5047</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>999</v>
+        <v>912</v>
       </c>
       <c r="C6" t="n">
-        <v>4812</v>
+        <v>4124</v>
       </c>
       <c r="D6" t="n">
-        <v>1406</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>474</v>
+        <v>433</v>
       </c>
       <c r="C7" t="n">
-        <v>2597</v>
+        <v>2408</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C8" t="n">
-        <v>1372</v>
+        <v>1185</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>592</v>
+        <v>499</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3500</v>
+        <v>2077</v>
       </c>
       <c r="C2" t="n">
-        <v>3437</v>
+        <v>2030</v>
       </c>
       <c r="D2" t="n">
-        <v>21863</v>
+        <v>13262</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4216</v>
+        <v>3425</v>
       </c>
       <c r="C3" t="n">
-        <v>5750</v>
+        <v>5921</v>
       </c>
       <c r="D3" t="n">
-        <v>21362</v>
+        <v>18774</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3411</v>
+        <v>3096</v>
       </c>
       <c r="C4" t="n">
-        <v>8640</v>
+        <v>9280</v>
       </c>
       <c r="D4" t="n">
-        <v>14198</v>
+        <v>13334</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1762</v>
+        <v>1597</v>
       </c>
       <c r="C5" t="n">
-        <v>9648</v>
+        <v>8340</v>
       </c>
       <c r="D5" t="n">
-        <v>5187</v>
+        <v>5316</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>825</v>
+        <v>770</v>
       </c>
       <c r="C6" t="n">
-        <v>5485</v>
+        <v>4988</v>
       </c>
       <c r="D6" t="n">
-        <v>1354</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C7" t="n">
-        <v>2634</v>
+        <v>2405</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>970</v>
+        <v>849</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3535</v>
+        <v>3127</v>
       </c>
       <c r="C2" t="n">
-        <v>11830</v>
+        <v>7311</v>
       </c>
       <c r="D2" t="n">
-        <v>21701</v>
+        <v>12290</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3354</v>
+        <v>2461</v>
       </c>
       <c r="C3" t="n">
-        <v>4245</v>
+        <v>3710</v>
       </c>
       <c r="D3" t="n">
-        <v>20024</v>
+        <v>16942</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3247</v>
+        <v>2852</v>
       </c>
       <c r="C4" t="n">
-        <v>7239</v>
+        <v>7595</v>
       </c>
       <c r="D4" t="n">
-        <v>14866</v>
+        <v>13764</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2127</v>
+        <v>1941</v>
       </c>
       <c r="C5" t="n">
-        <v>9021</v>
+        <v>8661</v>
       </c>
       <c r="D5" t="n">
-        <v>6376</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1060</v>
+        <v>976</v>
       </c>
       <c r="C6" t="n">
-        <v>7169</v>
+        <v>6375</v>
       </c>
       <c r="D6" t="n">
-        <v>1815</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="C7" t="n">
-        <v>3774</v>
+        <v>3440</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>708</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>1559</v>
+        <v>1437</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>488</v>
+        <v>444</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
         <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2374</v>
+        <v>2179</v>
       </c>
       <c r="C2" t="n">
-        <v>6232</v>
+        <v>5021</v>
       </c>
       <c r="D2" t="n">
-        <v>16735</v>
+        <v>9552</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2990</v>
+        <v>2343</v>
       </c>
       <c r="C3" t="n">
-        <v>6420</v>
+        <v>4639</v>
       </c>
       <c r="D3" t="n">
-        <v>19154</v>
+        <v>15462</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3013</v>
+        <v>2524</v>
       </c>
       <c r="C4" t="n">
-        <v>6147</v>
+        <v>6089</v>
       </c>
       <c r="D4" t="n">
-        <v>15200</v>
+        <v>14036</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2302</v>
+        <v>2112</v>
       </c>
       <c r="C5" t="n">
-        <v>8581</v>
+        <v>8434</v>
       </c>
       <c r="D5" t="n">
-        <v>7201</v>
+        <v>6964</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1223</v>
+        <v>1138</v>
       </c>
       <c r="C6" t="n">
-        <v>7991</v>
+        <v>7325</v>
       </c>
       <c r="D6" t="n">
-        <v>2179</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C7" t="n">
-        <v>4726</v>
+        <v>4331</v>
       </c>
       <c r="D7" t="n">
-        <v>750</v>
+        <v>794</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>2033</v>
+        <v>1913</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>539</v>
+        <v>514</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3115</v>
+        <v>3129</v>
       </c>
       <c r="C2" t="n">
-        <v>9770</v>
+        <v>6818</v>
       </c>
       <c r="D2" t="n">
-        <v>14621</v>
+        <v>9156</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2346</v>
+        <v>1925</v>
       </c>
       <c r="C3" t="n">
-        <v>5730</v>
+        <v>4261</v>
       </c>
       <c r="D3" t="n">
-        <v>17687</v>
+        <v>13763</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2637</v>
+        <v>2139</v>
       </c>
       <c r="C4" t="n">
-        <v>6067</v>
+        <v>5349</v>
       </c>
       <c r="D4" t="n">
-        <v>15269</v>
+        <v>13814</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2305</v>
+        <v>2056</v>
       </c>
       <c r="C5" t="n">
-        <v>7467</v>
+        <v>7313</v>
       </c>
       <c r="D5" t="n">
-        <v>7911</v>
+        <v>7702</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1453</v>
+        <v>1362</v>
       </c>
       <c r="C6" t="n">
-        <v>8142</v>
+        <v>7689</v>
       </c>
       <c r="D6" t="n">
-        <v>2777</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C7" t="n">
-        <v>5922</v>
+        <v>5486</v>
       </c>
       <c r="D7" t="n">
-        <v>910</v>
+        <v>969</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>2903</v>
+        <v>2741</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>997</v>
+        <v>971</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D10" t="n">
         <v>186</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6459</v>
+        <v>5220</v>
       </c>
       <c r="C2" t="n">
-        <v>5798</v>
+        <v>2424</v>
       </c>
       <c r="D2" t="n">
-        <v>8462</v>
+        <v>14145</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2277</v>
+        <v>2261</v>
       </c>
       <c r="C2" t="n">
-        <v>5784</v>
+        <v>3927</v>
       </c>
       <c r="D2" t="n">
-        <v>10878</v>
+        <v>6812</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3121</v>
+        <v>2582</v>
       </c>
       <c r="C3" t="n">
-        <v>7151</v>
+        <v>5208</v>
       </c>
       <c r="D3" t="n">
-        <v>18970</v>
+        <v>14653</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3456</v>
+        <v>2991</v>
       </c>
       <c r="C4" t="n">
-        <v>8715</v>
+        <v>7860</v>
       </c>
       <c r="D4" t="n">
-        <v>15384</v>
+        <v>14181</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1363</v>
+        <v>1296</v>
       </c>
       <c r="C5" t="n">
-        <v>11282</v>
+        <v>10807</v>
       </c>
       <c r="D5" t="n">
-        <v>7083</v>
+        <v>6967</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C6" t="n">
-        <v>7160</v>
+        <v>6807</v>
       </c>
       <c r="D6" t="n">
-        <v>2118</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>2844</v>
+        <v>2686</v>
       </c>
       <c r="D7" t="n">
-        <v>535</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>977</v>
+        <v>951</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D9" t="n">
         <v>182</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8405</v>
+        <v>5897</v>
       </c>
       <c r="C2" t="n">
-        <v>6783</v>
+        <v>5577</v>
       </c>
       <c r="D2" t="n">
-        <v>28480</v>
+        <v>14196</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2744</v>
+        <v>2218</v>
       </c>
       <c r="C3" t="n">
-        <v>2922</v>
+        <v>1221</v>
       </c>
       <c r="D3" t="n">
-        <v>2060</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5036</v>
+        <v>4312</v>
       </c>
       <c r="C2" t="n">
-        <v>5155</v>
+        <v>4919</v>
       </c>
       <c r="D2" t="n">
-        <v>30367</v>
+        <v>31086</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4574</v>
+        <v>3331</v>
       </c>
       <c r="C3" t="n">
-        <v>4404</v>
+        <v>3211</v>
       </c>
       <c r="D3" t="n">
-        <v>6346</v>
+        <v>4671</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1226</v>
+        <v>997</v>
       </c>
       <c r="C4" t="n">
-        <v>1755</v>
+        <v>770</v>
       </c>
       <c r="D4" t="n">
-        <v>1596</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4477</v>
+        <v>4366</v>
       </c>
       <c r="C2" t="n">
-        <v>8516</v>
+        <v>7618</v>
       </c>
       <c r="D2" t="n">
-        <v>23982</v>
+        <v>35322</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3961</v>
+        <v>3137</v>
       </c>
       <c r="C3" t="n">
-        <v>4208</v>
+        <v>3585</v>
       </c>
       <c r="D3" t="n">
-        <v>9732</v>
+        <v>8561</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2463</v>
+        <v>1832</v>
       </c>
       <c r="C4" t="n">
-        <v>3176</v>
+        <v>2136</v>
       </c>
       <c r="D4" t="n">
-        <v>2459</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>552</v>
+        <v>470</v>
       </c>
       <c r="C5" t="n">
-        <v>1056</v>
+        <v>514</v>
       </c>
       <c r="D5" t="n">
-        <v>1222</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5170</v>
+        <v>4600</v>
       </c>
       <c r="C2" t="n">
-        <v>6933</v>
+        <v>9529</v>
       </c>
       <c r="D2" t="n">
-        <v>27296</v>
+        <v>28270</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3469</v>
+        <v>3058</v>
       </c>
       <c r="C3" t="n">
-        <v>5592</v>
+        <v>4927</v>
       </c>
       <c r="D3" t="n">
-        <v>11212</v>
+        <v>12025</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2706</v>
+        <v>2099</v>
       </c>
       <c r="C4" t="n">
-        <v>3664</v>
+        <v>2850</v>
       </c>
       <c r="D4" t="n">
-        <v>3710</v>
+        <v>3339</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1235</v>
+        <v>961</v>
       </c>
       <c r="C5" t="n">
-        <v>2133</v>
+        <v>1359</v>
       </c>
       <c r="D5" t="n">
-        <v>1386</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="C6" t="n">
-        <v>673</v>
+        <v>407</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5958</v>
+        <v>6190</v>
       </c>
       <c r="C2" t="n">
-        <v>11138</v>
+        <v>8413</v>
       </c>
       <c r="D2" t="n">
-        <v>29289</v>
+        <v>34309</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3123</v>
+        <v>2783</v>
       </c>
       <c r="C3" t="n">
-        <v>5142</v>
+        <v>5995</v>
       </c>
       <c r="D3" t="n">
-        <v>12106</v>
+        <v>12840</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1921</v>
+        <v>1611</v>
       </c>
       <c r="C4" t="n">
-        <v>3872</v>
+        <v>3293</v>
       </c>
       <c r="D4" t="n">
-        <v>4332</v>
+        <v>4182</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1020</v>
+        <v>798</v>
       </c>
       <c r="C5" t="n">
-        <v>2137</v>
+        <v>1571</v>
       </c>
       <c r="D5" t="n">
-        <v>1402</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>358</v>
+        <v>293</v>
       </c>
       <c r="C6" t="n">
-        <v>934</v>
+        <v>594</v>
       </c>
       <c r="D6" t="n">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>326</v>
+        <v>243</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6490</v>
+        <v>4907</v>
       </c>
       <c r="C2" t="n">
-        <v>11602</v>
+        <v>5616</v>
       </c>
       <c r="D2" t="n">
-        <v>31738</v>
+        <v>29107</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3755</v>
+        <v>3738</v>
       </c>
       <c r="C3" t="n">
-        <v>7439</v>
+        <v>6379</v>
       </c>
       <c r="D3" t="n">
-        <v>14101</v>
+        <v>15652</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2185</v>
+        <v>1929</v>
       </c>
       <c r="C4" t="n">
-        <v>4559</v>
+        <v>4884</v>
       </c>
       <c r="D4" t="n">
-        <v>5725</v>
+        <v>5883</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1315</v>
+        <v>1068</v>
       </c>
       <c r="C5" t="n">
-        <v>3108</v>
+        <v>2563</v>
       </c>
       <c r="D5" t="n">
-        <v>1950</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>637</v>
+        <v>509</v>
       </c>
       <c r="C6" t="n">
-        <v>1603</v>
+        <v>1149</v>
       </c>
       <c r="D6" t="n">
-        <v>885</v>
+        <v>875</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>203</v>
+        <v>174</v>
       </c>
       <c r="C7" t="n">
-        <v>665</v>
+        <v>442</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6282</v>
+        <v>3752</v>
       </c>
       <c r="C2" t="n">
-        <v>9368</v>
+        <v>5164</v>
       </c>
       <c r="D2" t="n">
-        <v>41160</v>
+        <v>22756</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4155</v>
+        <v>3587</v>
       </c>
       <c r="C3" t="n">
-        <v>8382</v>
+        <v>5161</v>
       </c>
       <c r="D3" t="n">
-        <v>15907</v>
+        <v>16677</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2522</v>
+        <v>2415</v>
       </c>
       <c r="C4" t="n">
-        <v>6067</v>
+        <v>5582</v>
       </c>
       <c r="D4" t="n">
-        <v>7159</v>
+        <v>7579</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1543</v>
+        <v>1321</v>
       </c>
       <c r="C5" t="n">
-        <v>3793</v>
+        <v>3802</v>
       </c>
       <c r="D5" t="n">
-        <v>2579</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>876</v>
+        <v>712</v>
       </c>
       <c r="C6" t="n">
-        <v>2379</v>
+        <v>1895</v>
       </c>
       <c r="D6" t="n">
-        <v>1048</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>367</v>
+        <v>303</v>
       </c>
       <c r="C7" t="n">
-        <v>1151</v>
+        <v>815</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>470</v>
+        <v>337</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
         <v>241</v>
@@ -6510,7 +6510,7 @@
         <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6650,7 +6650,7 @@
         <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_73_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_73_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5384</v>
+        <v>4953</v>
       </c>
       <c r="C2" t="n">
-        <v>4358</v>
+        <v>10292</v>
       </c>
       <c r="D2" t="n">
-        <v>21742</v>
+        <v>18395</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3031</v>
+        <v>3595</v>
       </c>
       <c r="C3" t="n">
-        <v>4501</v>
+        <v>6404</v>
       </c>
       <c r="D3" t="n">
-        <v>16426</v>
+        <v>12667</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2558</v>
+        <v>2849</v>
       </c>
       <c r="C4" t="n">
-        <v>5243</v>
+        <v>6624</v>
       </c>
       <c r="D4" t="n">
-        <v>9008</v>
+        <v>6641</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1601</v>
+        <v>1748</v>
       </c>
       <c r="C5" t="n">
-        <v>4592</v>
+        <v>4769</v>
       </c>
       <c r="D5" t="n">
-        <v>3320</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>906</v>
+        <v>920</v>
       </c>
       <c r="C6" t="n">
-        <v>2826</v>
+        <v>3301</v>
       </c>
       <c r="D6" t="n">
-        <v>1295</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C7" t="n">
-        <v>1343</v>
+        <v>2272</v>
       </c>
       <c r="D7" t="n">
-        <v>675</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C8" t="n">
-        <v>558</v>
+        <v>1197</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -881,10 +881,10 @@
         <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>274</v>
+        <v>469</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5353</v>
+        <v>5719</v>
       </c>
       <c r="C2" t="n">
-        <v>14888</v>
+        <v>11743</v>
       </c>
       <c r="D2" t="n">
-        <v>31413</v>
+        <v>22657</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3306</v>
+        <v>3462</v>
       </c>
       <c r="C3" t="n">
-        <v>3895</v>
+        <v>7169</v>
       </c>
       <c r="D3" t="n">
-        <v>16045</v>
+        <v>12594</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2370</v>
+        <v>2705</v>
       </c>
       <c r="C4" t="n">
-        <v>4770</v>
+        <v>6382</v>
       </c>
       <c r="D4" t="n">
-        <v>9858</v>
+        <v>7422</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1781</v>
+        <v>1948</v>
       </c>
       <c r="C5" t="n">
-        <v>4758</v>
+        <v>5460</v>
       </c>
       <c r="D5" t="n">
-        <v>4147</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1110</v>
+        <v>1149</v>
       </c>
       <c r="C6" t="n">
-        <v>3611</v>
+        <v>3917</v>
       </c>
       <c r="D6" t="n">
-        <v>1575</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="C7" t="n">
-        <v>1997</v>
+        <v>2692</v>
       </c>
       <c r="D7" t="n">
-        <v>765</v>
+        <v>706</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
-        <v>903</v>
+        <v>1649</v>
       </c>
       <c r="D8" t="n">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1192,10 +1192,10 @@
         <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>390</v>
+        <v>756</v>
       </c>
       <c r="D9" t="n">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>321</v>
       </c>
       <c r="D10" t="n">
         <v>248</v>
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7346</v>
+        <v>7002</v>
       </c>
       <c r="C2" t="n">
-        <v>16970</v>
+        <v>15516</v>
       </c>
       <c r="D2" t="n">
-        <v>42535</v>
+        <v>20523</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3388</v>
+        <v>3551</v>
       </c>
       <c r="C3" t="n">
-        <v>7497</v>
+        <v>7987</v>
       </c>
       <c r="D3" t="n">
-        <v>16959</v>
+        <v>12995</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2370</v>
+        <v>2566</v>
       </c>
       <c r="C4" t="n">
-        <v>4238</v>
+        <v>6520</v>
       </c>
       <c r="D4" t="n">
-        <v>10508</v>
+        <v>7869</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1800</v>
+        <v>2017</v>
       </c>
       <c r="C5" t="n">
-        <v>4618</v>
+        <v>5727</v>
       </c>
       <c r="D5" t="n">
-        <v>4803</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1259</v>
+        <v>1323</v>
       </c>
       <c r="C6" t="n">
-        <v>4062</v>
+        <v>4452</v>
       </c>
       <c r="D6" t="n">
-        <v>1924</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="C7" t="n">
-        <v>2640</v>
+        <v>3144</v>
       </c>
       <c r="D7" t="n">
-        <v>860</v>
+        <v>787</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C8" t="n">
-        <v>1342</v>
+        <v>2046</v>
       </c>
       <c r="D8" t="n">
-        <v>499</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" t="n">
-        <v>582</v>
+        <v>1072</v>
       </c>
       <c r="D9" t="n">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>471</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6606</v>
+        <v>6426</v>
       </c>
       <c r="C2" t="n">
-        <v>11539</v>
+        <v>10799</v>
       </c>
       <c r="D2" t="n">
-        <v>34679</v>
+        <v>17042</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4184</v>
+        <v>4394</v>
       </c>
       <c r="C3" t="n">
-        <v>10942</v>
+        <v>12035</v>
       </c>
       <c r="D3" t="n">
-        <v>18756</v>
+        <v>14268</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1663</v>
+        <v>1863</v>
       </c>
       <c r="C4" t="n">
-        <v>6792</v>
+        <v>9003</v>
       </c>
       <c r="D4" t="n">
-        <v>10280</v>
+        <v>7655</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1163</v>
+        <v>1222</v>
       </c>
       <c r="C5" t="n">
-        <v>3980</v>
+        <v>4362</v>
       </c>
       <c r="D5" t="n">
-        <v>3176</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="C6" t="n">
-        <v>2587</v>
+        <v>3081</v>
       </c>
       <c r="D6" t="n">
-        <v>842</v>
+        <v>771</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C7" t="n">
-        <v>1315</v>
+        <v>2005</v>
       </c>
       <c r="D7" t="n">
-        <v>489</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>570</v>
+        <v>1050</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>461</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3933</v>
+        <v>3975</v>
       </c>
       <c r="C2" t="n">
-        <v>5509</v>
+        <v>5307</v>
       </c>
       <c r="D2" t="n">
-        <v>23730</v>
+        <v>13003</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4483</v>
+        <v>4513</v>
       </c>
       <c r="C3" t="n">
-        <v>10157</v>
+        <v>10443</v>
       </c>
       <c r="D3" t="n">
-        <v>19841</v>
+        <v>13960</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2310</v>
+        <v>2441</v>
       </c>
       <c r="C4" t="n">
-        <v>8863</v>
+        <v>10443</v>
       </c>
       <c r="D4" t="n">
-        <v>11466</v>
+        <v>8448</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1278</v>
+        <v>1363</v>
       </c>
       <c r="C5" t="n">
-        <v>5249</v>
+        <v>6351</v>
       </c>
       <c r="D5" t="n">
-        <v>4027</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="C6" t="n">
-        <v>3200</v>
+        <v>3669</v>
       </c>
       <c r="D6" t="n">
-        <v>1080</v>
+        <v>934</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="C7" t="n">
-        <v>1779</v>
+        <v>2465</v>
       </c>
       <c r="D7" t="n">
-        <v>536</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>774</v>
+        <v>1348</v>
       </c>
       <c r="D8" t="n">
-        <v>343</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>331</v>
+        <v>510</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3498</v>
+        <v>3850</v>
       </c>
       <c r="C2" t="n">
-        <v>4293</v>
+        <v>14520</v>
       </c>
       <c r="D2" t="n">
-        <v>19021</v>
+        <v>19548</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3568</v>
+        <v>3642</v>
       </c>
       <c r="C3" t="n">
-        <v>7069</v>
+        <v>7177</v>
       </c>
       <c r="D3" t="n">
-        <v>19226</v>
+        <v>12891</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2804</v>
+        <v>2827</v>
       </c>
       <c r="C4" t="n">
-        <v>9312</v>
+        <v>10225</v>
       </c>
       <c r="D4" t="n">
-        <v>12484</v>
+        <v>9090</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1523</v>
+        <v>1608</v>
       </c>
       <c r="C5" t="n">
-        <v>6839</v>
+        <v>8165</v>
       </c>
       <c r="D5" t="n">
-        <v>5047</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>912</v>
+        <v>938</v>
       </c>
       <c r="C6" t="n">
-        <v>4124</v>
+        <v>4793</v>
       </c>
       <c r="D6" t="n">
-        <v>1490</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="C7" t="n">
-        <v>2408</v>
+        <v>2995</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C8" t="n">
-        <v>1185</v>
+        <v>1798</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>499</v>
+        <v>818</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>259</v>
+        <v>333</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D16" t="n">
         <v>36</v>
-      </c>
-      <c r="D16" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2077</v>
+        <v>2338</v>
       </c>
       <c r="C2" t="n">
-        <v>2030</v>
+        <v>7001</v>
       </c>
       <c r="D2" t="n">
-        <v>13262</v>
+        <v>13633</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3425</v>
+        <v>3562</v>
       </c>
       <c r="C3" t="n">
-        <v>5921</v>
+        <v>9262</v>
       </c>
       <c r="D3" t="n">
-        <v>18774</v>
+        <v>13294</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3096</v>
+        <v>3107</v>
       </c>
       <c r="C4" t="n">
-        <v>9280</v>
+        <v>10126</v>
       </c>
       <c r="D4" t="n">
-        <v>13334</v>
+        <v>9615</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1597</v>
+        <v>1652</v>
       </c>
       <c r="C5" t="n">
-        <v>8340</v>
+        <v>9816</v>
       </c>
       <c r="D5" t="n">
-        <v>5316</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="C6" t="n">
-        <v>4988</v>
+        <v>5679</v>
       </c>
       <c r="D6" t="n">
-        <v>1447</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C7" t="n">
-        <v>2405</v>
+        <v>3170</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>849</v>
+        <v>1330</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>253</v>
+        <v>326</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
         <v>165</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>34</v>
+      </c>
+      <c r="D15" t="n">
         <v>35</v>
-      </c>
-      <c r="D15" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3127</v>
+        <v>2540</v>
       </c>
       <c r="C2" t="n">
-        <v>7311</v>
+        <v>10058</v>
       </c>
       <c r="D2" t="n">
-        <v>12290</v>
+        <v>12265</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2461</v>
+        <v>2629</v>
       </c>
       <c r="C3" t="n">
-        <v>3710</v>
+        <v>7367</v>
       </c>
       <c r="D3" t="n">
-        <v>16942</v>
+        <v>12465</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2852</v>
+        <v>2900</v>
       </c>
       <c r="C4" t="n">
-        <v>7595</v>
+        <v>9614</v>
       </c>
       <c r="D4" t="n">
-        <v>13764</v>
+        <v>9887</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1941</v>
+        <v>1968</v>
       </c>
       <c r="C5" t="n">
-        <v>8661</v>
+        <v>9839</v>
       </c>
       <c r="D5" t="n">
-        <v>6308</v>
+        <v>4741</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="C6" t="n">
-        <v>6375</v>
+        <v>7352</v>
       </c>
       <c r="D6" t="n">
-        <v>1948</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C7" t="n">
-        <v>3440</v>
+        <v>4189</v>
       </c>
       <c r="D7" t="n">
-        <v>708</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>1437</v>
+        <v>1986</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>444</v>
+        <v>637</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
+        <v>131</v>
+      </c>
+      <c r="D11" t="n">
         <v>135</v>
-      </c>
-      <c r="D11" t="n">
-        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>58</v>
+      </c>
+      <c r="D13" t="n">
         <v>60</v>
-      </c>
-      <c r="D13" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2179</v>
+        <v>1718</v>
       </c>
       <c r="C2" t="n">
-        <v>5021</v>
+        <v>6484</v>
       </c>
       <c r="D2" t="n">
-        <v>9552</v>
+        <v>9435</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2343</v>
+        <v>2283</v>
       </c>
       <c r="C3" t="n">
-        <v>4639</v>
+        <v>7703</v>
       </c>
       <c r="D3" t="n">
-        <v>15462</v>
+        <v>11784</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2524</v>
+        <v>2579</v>
       </c>
       <c r="C4" t="n">
-        <v>6089</v>
+        <v>8735</v>
       </c>
       <c r="D4" t="n">
-        <v>14036</v>
+        <v>10003</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2112</v>
+        <v>2137</v>
       </c>
       <c r="C5" t="n">
-        <v>8434</v>
+        <v>9934</v>
       </c>
       <c r="D5" t="n">
-        <v>6964</v>
+        <v>5231</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1138</v>
+        <v>1132</v>
       </c>
       <c r="C6" t="n">
-        <v>7325</v>
+        <v>8381</v>
       </c>
       <c r="D6" t="n">
-        <v>2358</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="C7" t="n">
-        <v>4331</v>
+        <v>5187</v>
       </c>
       <c r="D7" t="n">
-        <v>794</v>
+        <v>706</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1913</v>
+        <v>2500</v>
       </c>
       <c r="D8" t="n">
-        <v>417</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>514</v>
+        <v>696</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3129</v>
+        <v>2806</v>
       </c>
       <c r="C2" t="n">
-        <v>6818</v>
+        <v>7203</v>
       </c>
       <c r="D2" t="n">
-        <v>9156</v>
+        <v>9310</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1925</v>
+        <v>1764</v>
       </c>
       <c r="C3" t="n">
-        <v>4261</v>
+        <v>6467</v>
       </c>
       <c r="D3" t="n">
-        <v>13763</v>
+        <v>10785</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2139</v>
+        <v>2155</v>
       </c>
       <c r="C4" t="n">
-        <v>5349</v>
+        <v>8137</v>
       </c>
       <c r="D4" t="n">
-        <v>13814</v>
+        <v>9938</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2056</v>
+        <v>2105</v>
       </c>
       <c r="C5" t="n">
-        <v>7313</v>
+        <v>9266</v>
       </c>
       <c r="D5" t="n">
-        <v>7702</v>
+        <v>5617</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1362</v>
+        <v>1346</v>
       </c>
       <c r="C6" t="n">
-        <v>7689</v>
+        <v>8880</v>
       </c>
       <c r="D6" t="n">
-        <v>2902</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>479</v>
+        <v>451</v>
       </c>
       <c r="C7" t="n">
-        <v>5486</v>
+        <v>6311</v>
       </c>
       <c r="D7" t="n">
-        <v>969</v>
+        <v>833</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>2741</v>
+        <v>3418</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>971</v>
+        <v>1250</v>
       </c>
       <c r="D9" t="n">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>306</v>
+        <v>360</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5220</v>
+        <v>5981</v>
       </c>
       <c r="C2" t="n">
-        <v>2424</v>
+        <v>11882</v>
       </c>
       <c r="D2" t="n">
-        <v>14145</v>
+        <v>11273</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2261</v>
+        <v>2050</v>
       </c>
       <c r="C2" t="n">
-        <v>3927</v>
+        <v>4265</v>
       </c>
       <c r="D2" t="n">
-        <v>6812</v>
+        <v>6926</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2582</v>
+        <v>2439</v>
       </c>
       <c r="C3" t="n">
-        <v>5208</v>
+        <v>7287</v>
       </c>
       <c r="D3" t="n">
-        <v>14653</v>
+        <v>11638</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2991</v>
+        <v>3027</v>
       </c>
       <c r="C4" t="n">
-        <v>7860</v>
+        <v>11343</v>
       </c>
       <c r="D4" t="n">
-        <v>14181</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1296</v>
+        <v>1263</v>
       </c>
       <c r="C5" t="n">
-        <v>10807</v>
+        <v>12917</v>
       </c>
       <c r="D5" t="n">
-        <v>6967</v>
+        <v>5167</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="C6" t="n">
-        <v>6807</v>
+        <v>7751</v>
       </c>
       <c r="D6" t="n">
-        <v>2248</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>2686</v>
+        <v>3349</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>951</v>
+        <v>1225</v>
       </c>
       <c r="D8" t="n">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>299</v>
+        <v>352</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5897</v>
+        <v>6489</v>
       </c>
       <c r="C2" t="n">
-        <v>5577</v>
+        <v>8504</v>
       </c>
       <c r="D2" t="n">
-        <v>14196</v>
+        <v>16863</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2218</v>
+        <v>2541</v>
       </c>
       <c r="C3" t="n">
-        <v>1221</v>
+        <v>5988</v>
       </c>
       <c r="D3" t="n">
-        <v>3015</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4312</v>
+        <v>4257</v>
       </c>
       <c r="C2" t="n">
-        <v>4919</v>
+        <v>4979</v>
       </c>
       <c r="D2" t="n">
-        <v>31086</v>
+        <v>16821</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3331</v>
+        <v>3708</v>
       </c>
       <c r="C3" t="n">
-        <v>3211</v>
+        <v>6391</v>
       </c>
       <c r="D3" t="n">
-        <v>4671</v>
+        <v>4754</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>997</v>
+        <v>1138</v>
       </c>
       <c r="C4" t="n">
-        <v>770</v>
+        <v>3552</v>
       </c>
       <c r="D4" t="n">
-        <v>1789</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4366</v>
+        <v>3756</v>
       </c>
       <c r="C2" t="n">
-        <v>7618</v>
+        <v>5974</v>
       </c>
       <c r="D2" t="n">
-        <v>35322</v>
+        <v>19030</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3137</v>
+        <v>3279</v>
       </c>
       <c r="C3" t="n">
-        <v>3585</v>
+        <v>4887</v>
       </c>
       <c r="D3" t="n">
-        <v>8561</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1832</v>
+        <v>2061</v>
       </c>
       <c r="C4" t="n">
-        <v>2136</v>
+        <v>5024</v>
       </c>
       <c r="D4" t="n">
-        <v>2287</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>470</v>
+        <v>518</v>
       </c>
       <c r="C5" t="n">
-        <v>514</v>
+        <v>2040</v>
       </c>
       <c r="D5" t="n">
-        <v>1248</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4600</v>
+        <v>5788</v>
       </c>
       <c r="C2" t="n">
-        <v>9529</v>
+        <v>6608</v>
       </c>
       <c r="D2" t="n">
-        <v>28270</v>
+        <v>29849</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3058</v>
+        <v>2890</v>
       </c>
       <c r="C3" t="n">
-        <v>4927</v>
+        <v>4739</v>
       </c>
       <c r="D3" t="n">
-        <v>12025</v>
+        <v>7824</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2099</v>
+        <v>2250</v>
       </c>
       <c r="C4" t="n">
-        <v>2850</v>
+        <v>4798</v>
       </c>
       <c r="D4" t="n">
-        <v>3339</v>
+        <v>2909</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>961</v>
+        <v>1063</v>
       </c>
       <c r="C5" t="n">
-        <v>1359</v>
+        <v>3544</v>
       </c>
       <c r="D5" t="n">
-        <v>1399</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="C6" t="n">
-        <v>407</v>
+        <v>1167</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>952</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6190</v>
+        <v>7677</v>
       </c>
       <c r="C2" t="n">
-        <v>8413</v>
+        <v>11275</v>
       </c>
       <c r="D2" t="n">
-        <v>34309</v>
+        <v>24278</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2783</v>
+        <v>3087</v>
       </c>
       <c r="C3" t="n">
-        <v>5995</v>
+        <v>4652</v>
       </c>
       <c r="D3" t="n">
-        <v>12840</v>
+        <v>9991</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1611</v>
+        <v>1579</v>
       </c>
       <c r="C4" t="n">
-        <v>3293</v>
+        <v>3898</v>
       </c>
       <c r="D4" t="n">
-        <v>4182</v>
+        <v>3242</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>798</v>
+        <v>859</v>
       </c>
       <c r="C5" t="n">
-        <v>1571</v>
+        <v>3022</v>
       </c>
       <c r="D5" t="n">
-        <v>1386</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="6">
@@ -5812,10 +5812,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="C6" t="n">
-        <v>594</v>
+        <v>1576</v>
       </c>
       <c r="D6" t="n">
         <v>777</v>
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>243</v>
+        <v>471</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4907</v>
+        <v>5405</v>
       </c>
       <c r="C2" t="n">
-        <v>5616</v>
+        <v>10143</v>
       </c>
       <c r="D2" t="n">
-        <v>29107</v>
+        <v>19561</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3738</v>
+        <v>4456</v>
       </c>
       <c r="C3" t="n">
-        <v>6379</v>
+        <v>7379</v>
       </c>
       <c r="D3" t="n">
-        <v>15652</v>
+        <v>11655</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1929</v>
+        <v>2040</v>
       </c>
       <c r="C4" t="n">
-        <v>4884</v>
+        <v>4228</v>
       </c>
       <c r="D4" t="n">
-        <v>5883</v>
+        <v>4472</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1068</v>
+        <v>1077</v>
       </c>
       <c r="C5" t="n">
-        <v>2563</v>
+        <v>3472</v>
       </c>
       <c r="D5" t="n">
-        <v>1907</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>509</v>
+        <v>544</v>
       </c>
       <c r="C6" t="n">
-        <v>1149</v>
+        <v>2375</v>
       </c>
       <c r="D6" t="n">
-        <v>875</v>
+        <v>861</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>442</v>
+        <v>1088</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>233</v>
+        <v>356</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3752</v>
+        <v>4725</v>
       </c>
       <c r="C2" t="n">
-        <v>5164</v>
+        <v>6931</v>
       </c>
       <c r="D2" t="n">
-        <v>22756</v>
+        <v>21934</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3587</v>
+        <v>4049</v>
       </c>
       <c r="C3" t="n">
-        <v>5161</v>
+        <v>7681</v>
       </c>
       <c r="D3" t="n">
-        <v>16677</v>
+        <v>12080</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2415</v>
+        <v>2743</v>
       </c>
       <c r="C4" t="n">
-        <v>5582</v>
+        <v>5894</v>
       </c>
       <c r="D4" t="n">
-        <v>7579</v>
+        <v>5715</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1321</v>
+        <v>1364</v>
       </c>
       <c r="C5" t="n">
-        <v>3802</v>
+        <v>3806</v>
       </c>
       <c r="D5" t="n">
-        <v>2555</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>712</v>
+        <v>729</v>
       </c>
       <c r="C6" t="n">
-        <v>1895</v>
+        <v>2893</v>
       </c>
       <c r="D6" t="n">
-        <v>1050</v>
+        <v>973</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="C7" t="n">
-        <v>815</v>
+        <v>1756</v>
       </c>
       <c r="D7" t="n">
-        <v>608</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>337</v>
+        <v>721</v>
       </c>
       <c r="D8" t="n">
-        <v>416</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_73_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_73_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4953</v>
+        <v>781</v>
       </c>
       <c r="C2" t="n">
-        <v>10292</v>
+        <v>2182</v>
       </c>
       <c r="D2" t="n">
-        <v>18395</v>
+        <v>12482</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3595</v>
+        <v>1637</v>
       </c>
       <c r="C3" t="n">
-        <v>6404</v>
+        <v>6166</v>
       </c>
       <c r="D3" t="n">
-        <v>12667</v>
+        <v>12686</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2849</v>
+        <v>1343</v>
       </c>
       <c r="C4" t="n">
-        <v>6624</v>
+        <v>8425</v>
       </c>
       <c r="D4" t="n">
-        <v>6641</v>
+        <v>5839</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1748</v>
+        <v>699</v>
       </c>
       <c r="C5" t="n">
-        <v>4769</v>
+        <v>5806</v>
       </c>
       <c r="D5" t="n">
-        <v>2605</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>920</v>
+        <v>285</v>
       </c>
       <c r="C6" t="n">
-        <v>3301</v>
+        <v>2619</v>
       </c>
       <c r="D6" t="n">
-        <v>1143</v>
+        <v>728</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>449</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>2272</v>
+        <v>932</v>
       </c>
       <c r="D7" t="n">
-        <v>646</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>1197</v>
+        <v>369</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>469</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5719</v>
+        <v>743</v>
       </c>
       <c r="C2" t="n">
-        <v>11743</v>
+        <v>2478</v>
       </c>
       <c r="D2" t="n">
-        <v>22657</v>
+        <v>19154</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3462</v>
+        <v>1060</v>
       </c>
       <c r="C3" t="n">
-        <v>7169</v>
+        <v>3599</v>
       </c>
       <c r="D3" t="n">
-        <v>12594</v>
+        <v>11761</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2705</v>
+        <v>1279</v>
       </c>
       <c r="C4" t="n">
-        <v>6382</v>
+        <v>7035</v>
       </c>
       <c r="D4" t="n">
-        <v>7422</v>
+        <v>6910</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1948</v>
+        <v>886</v>
       </c>
       <c r="C5" t="n">
-        <v>5460</v>
+        <v>7098</v>
       </c>
       <c r="D5" t="n">
-        <v>3120</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1149</v>
+        <v>420</v>
       </c>
       <c r="C6" t="n">
-        <v>3917</v>
+        <v>4177</v>
       </c>
       <c r="D6" t="n">
-        <v>1352</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>584</v>
+        <v>157</v>
       </c>
       <c r="C7" t="n">
-        <v>2692</v>
+        <v>1734</v>
       </c>
       <c r="D7" t="n">
-        <v>706</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1649</v>
+        <v>620</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>756</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>321</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7002</v>
+        <v>402</v>
       </c>
       <c r="C2" t="n">
-        <v>15516</v>
+        <v>1050</v>
       </c>
       <c r="D2" t="n">
-        <v>20523</v>
+        <v>13063</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3551</v>
+        <v>936</v>
       </c>
       <c r="C3" t="n">
-        <v>7987</v>
+        <v>3024</v>
       </c>
       <c r="D3" t="n">
-        <v>12995</v>
+        <v>12347</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2566</v>
+        <v>1383</v>
       </c>
       <c r="C4" t="n">
-        <v>6520</v>
+        <v>6312</v>
       </c>
       <c r="D4" t="n">
-        <v>7869</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2017</v>
+        <v>889</v>
       </c>
       <c r="C5" t="n">
-        <v>5727</v>
+        <v>7997</v>
       </c>
       <c r="D5" t="n">
-        <v>3644</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1323</v>
+        <v>331</v>
       </c>
       <c r="C6" t="n">
-        <v>4452</v>
+        <v>5209</v>
       </c>
       <c r="D6" t="n">
-        <v>1558</v>
+        <v>917</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>717</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3144</v>
+        <v>1618</v>
       </c>
       <c r="D7" t="n">
-        <v>787</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>333</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>2046</v>
+        <v>528</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>1072</v>
+        <v>235</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>471</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>231</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6426</v>
+        <v>388</v>
       </c>
       <c r="C2" t="n">
-        <v>10799</v>
+        <v>5945</v>
       </c>
       <c r="D2" t="n">
-        <v>17042</v>
+        <v>15875</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4394</v>
+        <v>599</v>
       </c>
       <c r="C3" t="n">
-        <v>12035</v>
+        <v>1797</v>
       </c>
       <c r="D3" t="n">
-        <v>14268</v>
+        <v>11705</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1863</v>
+        <v>1049</v>
       </c>
       <c r="C4" t="n">
-        <v>9003</v>
+        <v>4536</v>
       </c>
       <c r="D4" t="n">
-        <v>7655</v>
+        <v>8143</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1222</v>
+        <v>1005</v>
       </c>
       <c r="C5" t="n">
-        <v>4362</v>
+        <v>7082</v>
       </c>
       <c r="D5" t="n">
-        <v>2506</v>
+        <v>3470</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>662</v>
+        <v>501</v>
       </c>
       <c r="C6" t="n">
-        <v>3081</v>
+        <v>6492</v>
       </c>
       <c r="D6" t="n">
-        <v>771</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>307</v>
+        <v>141</v>
       </c>
       <c r="C7" t="n">
-        <v>2005</v>
+        <v>3232</v>
       </c>
       <c r="D7" t="n">
-        <v>470</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1050</v>
+        <v>981</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>461</v>
+        <v>345</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3975</v>
+        <v>268</v>
       </c>
       <c r="C2" t="n">
-        <v>5307</v>
+        <v>3933</v>
       </c>
       <c r="D2" t="n">
-        <v>13003</v>
+        <v>11667</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4513</v>
+        <v>455</v>
       </c>
       <c r="C3" t="n">
-        <v>10443</v>
+        <v>3275</v>
       </c>
       <c r="D3" t="n">
-        <v>13960</v>
+        <v>11710</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2441</v>
+        <v>831</v>
       </c>
       <c r="C4" t="n">
-        <v>10443</v>
+        <v>3310</v>
       </c>
       <c r="D4" t="n">
-        <v>8448</v>
+        <v>8486</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1363</v>
+        <v>1012</v>
       </c>
       <c r="C5" t="n">
-        <v>6351</v>
+        <v>6155</v>
       </c>
       <c r="D5" t="n">
-        <v>3144</v>
+        <v>4014</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>792</v>
+        <v>607</v>
       </c>
       <c r="C6" t="n">
-        <v>3669</v>
+        <v>7032</v>
       </c>
       <c r="D6" t="n">
-        <v>934</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>288</v>
+        <v>155</v>
       </c>
       <c r="C7" t="n">
-        <v>2465</v>
+        <v>4378</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1348</v>
+        <v>1511</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>510</v>
+        <v>457</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3850</v>
+        <v>1005</v>
       </c>
       <c r="C2" t="n">
-        <v>14520</v>
+        <v>3750</v>
       </c>
       <c r="D2" t="n">
-        <v>19548</v>
+        <v>13230</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3642</v>
+        <v>320</v>
       </c>
       <c r="C3" t="n">
-        <v>7177</v>
+        <v>3145</v>
       </c>
       <c r="D3" t="n">
-        <v>12891</v>
+        <v>10917</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2827</v>
+        <v>594</v>
       </c>
       <c r="C4" t="n">
-        <v>10225</v>
+        <v>3256</v>
       </c>
       <c r="D4" t="n">
-        <v>9090</v>
+        <v>8754</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1608</v>
+        <v>876</v>
       </c>
       <c r="C5" t="n">
-        <v>8165</v>
+        <v>4743</v>
       </c>
       <c r="D5" t="n">
-        <v>3863</v>
+        <v>4578</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>938</v>
+        <v>708</v>
       </c>
       <c r="C6" t="n">
-        <v>4793</v>
+        <v>6587</v>
       </c>
       <c r="D6" t="n">
-        <v>1239</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>425</v>
+        <v>281</v>
       </c>
       <c r="C7" t="n">
-        <v>2995</v>
+        <v>5537</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>754</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1798</v>
+        <v>2649</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>818</v>
+        <v>843</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2338</v>
+        <v>683</v>
       </c>
       <c r="C2" t="n">
-        <v>7001</v>
+        <v>1980</v>
       </c>
       <c r="D2" t="n">
-        <v>13633</v>
+        <v>9525</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3562</v>
+        <v>560</v>
       </c>
       <c r="C3" t="n">
-        <v>9262</v>
+        <v>3556</v>
       </c>
       <c r="D3" t="n">
-        <v>13294</v>
+        <v>11958</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3107</v>
+        <v>1091</v>
       </c>
       <c r="C4" t="n">
-        <v>10126</v>
+        <v>4838</v>
       </c>
       <c r="D4" t="n">
-        <v>9615</v>
+        <v>8994</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1652</v>
+        <v>710</v>
       </c>
       <c r="C5" t="n">
-        <v>9816</v>
+        <v>8165</v>
       </c>
       <c r="D5" t="n">
-        <v>4066</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>765</v>
+        <v>259</v>
       </c>
       <c r="C6" t="n">
-        <v>5679</v>
+        <v>7040</v>
       </c>
       <c r="D6" t="n">
-        <v>1218</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>3170</v>
+        <v>2596</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1330</v>
+        <v>826</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>326</v>
+        <v>296</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2540</v>
+        <v>363</v>
       </c>
       <c r="C2" t="n">
-        <v>10058</v>
+        <v>2028</v>
       </c>
       <c r="D2" t="n">
-        <v>12265</v>
+        <v>6755</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2629</v>
+        <v>512</v>
       </c>
       <c r="C3" t="n">
-        <v>7367</v>
+        <v>2451</v>
       </c>
       <c r="D3" t="n">
-        <v>12465</v>
+        <v>10750</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2900</v>
+        <v>711</v>
       </c>
       <c r="C4" t="n">
-        <v>9614</v>
+        <v>3968</v>
       </c>
       <c r="D4" t="n">
-        <v>9887</v>
+        <v>8847</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1968</v>
+        <v>632</v>
       </c>
       <c r="C5" t="n">
-        <v>9839</v>
+        <v>5800</v>
       </c>
       <c r="D5" t="n">
-        <v>4741</v>
+        <v>4434</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>981</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>7352</v>
+        <v>6276</v>
       </c>
       <c r="D6" t="n">
-        <v>1596</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>60</v>
       </c>
       <c r="C7" t="n">
-        <v>4189</v>
+        <v>3259</v>
       </c>
       <c r="D7" t="n">
-        <v>636</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1986</v>
+        <v>980</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>637</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>126</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1718</v>
+        <v>326</v>
       </c>
       <c r="C2" t="n">
-        <v>6484</v>
+        <v>9859</v>
       </c>
       <c r="D2" t="n">
-        <v>9435</v>
+        <v>6583</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2283</v>
+        <v>369</v>
       </c>
       <c r="C3" t="n">
-        <v>7703</v>
+        <v>1921</v>
       </c>
       <c r="D3" t="n">
-        <v>11784</v>
+        <v>9336</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2579</v>
+        <v>536</v>
       </c>
       <c r="C4" t="n">
-        <v>8735</v>
+        <v>3064</v>
       </c>
       <c r="D4" t="n">
-        <v>10003</v>
+        <v>8943</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2137</v>
+        <v>611</v>
       </c>
       <c r="C5" t="n">
-        <v>9934</v>
+        <v>4694</v>
       </c>
       <c r="D5" t="n">
-        <v>5231</v>
+        <v>5104</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1132</v>
+        <v>392</v>
       </c>
       <c r="C6" t="n">
-        <v>8381</v>
+        <v>6020</v>
       </c>
       <c r="D6" t="n">
-        <v>1849</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>252</v>
+        <v>129</v>
       </c>
       <c r="C7" t="n">
-        <v>5187</v>
+        <v>4797</v>
       </c>
       <c r="D7" t="n">
-        <v>706</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>2500</v>
+        <v>2051</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>696</v>
+        <v>604</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2806</v>
+        <v>179</v>
       </c>
       <c r="C2" t="n">
-        <v>7203</v>
+        <v>13315</v>
       </c>
       <c r="D2" t="n">
-        <v>9310</v>
+        <v>13274</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1764</v>
+        <v>290</v>
       </c>
       <c r="C3" t="n">
-        <v>6467</v>
+        <v>5107</v>
       </c>
       <c r="D3" t="n">
-        <v>10785</v>
+        <v>8297</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2155</v>
+        <v>401</v>
       </c>
       <c r="C4" t="n">
-        <v>8137</v>
+        <v>2407</v>
       </c>
       <c r="D4" t="n">
-        <v>9938</v>
+        <v>8653</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2105</v>
+        <v>529</v>
       </c>
       <c r="C5" t="n">
-        <v>9266</v>
+        <v>3782</v>
       </c>
       <c r="D5" t="n">
-        <v>5617</v>
+        <v>5612</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1346</v>
+        <v>452</v>
       </c>
       <c r="C6" t="n">
-        <v>8880</v>
+        <v>5320</v>
       </c>
       <c r="D6" t="n">
-        <v>2247</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>451</v>
+        <v>215</v>
       </c>
       <c r="C7" t="n">
-        <v>6311</v>
+        <v>5323</v>
       </c>
       <c r="D7" t="n">
-        <v>833</v>
+        <v>928</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>3418</v>
+        <v>3314</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1250</v>
+        <v>1241</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5981</v>
+        <v>4734</v>
       </c>
       <c r="C2" t="n">
-        <v>11882</v>
+        <v>16619</v>
       </c>
       <c r="D2" t="n">
-        <v>11273</v>
+        <v>5517</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2050</v>
+        <v>814</v>
       </c>
       <c r="C2" t="n">
-        <v>4265</v>
+        <v>12040</v>
       </c>
       <c r="D2" t="n">
-        <v>6926</v>
+        <v>13061</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2439</v>
+        <v>204</v>
       </c>
       <c r="C3" t="n">
-        <v>7287</v>
+        <v>7719</v>
       </c>
       <c r="D3" t="n">
-        <v>11638</v>
+        <v>8416</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3027</v>
+        <v>309</v>
       </c>
       <c r="C4" t="n">
-        <v>11343</v>
+        <v>3627</v>
       </c>
       <c r="D4" t="n">
-        <v>10125</v>
+        <v>8331</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1263</v>
+        <v>436</v>
       </c>
       <c r="C5" t="n">
-        <v>12917</v>
+        <v>3046</v>
       </c>
       <c r="D5" t="n">
-        <v>5167</v>
+        <v>5854</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>416</v>
+        <v>453</v>
       </c>
       <c r="C6" t="n">
-        <v>7751</v>
+        <v>4589</v>
       </c>
       <c r="D6" t="n">
-        <v>1797</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>279</v>
       </c>
       <c r="C7" t="n">
-        <v>3349</v>
+        <v>5267</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>1225</v>
+        <v>4159</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>352</v>
+        <v>2073</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>86</v>
+        <v>217</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6489</v>
+        <v>4888</v>
       </c>
       <c r="C2" t="n">
-        <v>8504</v>
+        <v>12104</v>
       </c>
       <c r="D2" t="n">
-        <v>16863</v>
+        <v>16651</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2541</v>
+        <v>1564</v>
       </c>
       <c r="C3" t="n">
-        <v>5988</v>
+        <v>6562</v>
       </c>
       <c r="D3" t="n">
-        <v>2533</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4257</v>
+        <v>3281</v>
       </c>
       <c r="C2" t="n">
-        <v>4979</v>
+        <v>4425</v>
       </c>
       <c r="D2" t="n">
-        <v>16821</v>
+        <v>24778</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3708</v>
+        <v>2724</v>
       </c>
       <c r="C3" t="n">
-        <v>6391</v>
+        <v>8561</v>
       </c>
       <c r="D3" t="n">
-        <v>4754</v>
+        <v>3961</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1138</v>
+        <v>749</v>
       </c>
       <c r="C4" t="n">
-        <v>3552</v>
+        <v>4080</v>
       </c>
       <c r="D4" t="n">
-        <v>1691</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3756</v>
+        <v>2090</v>
       </c>
       <c r="C2" t="n">
-        <v>5974</v>
+        <v>6261</v>
       </c>
       <c r="D2" t="n">
-        <v>19030</v>
+        <v>24345</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3279</v>
+        <v>2475</v>
       </c>
       <c r="C3" t="n">
-        <v>4887</v>
+        <v>5317</v>
       </c>
       <c r="D3" t="n">
-        <v>6342</v>
+        <v>7166</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2061</v>
+        <v>1502</v>
       </c>
       <c r="C4" t="n">
-        <v>5024</v>
+        <v>6662</v>
       </c>
       <c r="D4" t="n">
-        <v>2227</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>518</v>
+        <v>367</v>
       </c>
       <c r="C5" t="n">
-        <v>2040</v>
+        <v>2433</v>
       </c>
       <c r="D5" t="n">
-        <v>1240</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5788</v>
+        <v>2270</v>
       </c>
       <c r="C2" t="n">
-        <v>6608</v>
+        <v>6327</v>
       </c>
       <c r="D2" t="n">
-        <v>29849</v>
+        <v>25658</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2890</v>
+        <v>1915</v>
       </c>
       <c r="C3" t="n">
-        <v>4739</v>
+        <v>5048</v>
       </c>
       <c r="D3" t="n">
-        <v>7824</v>
+        <v>9398</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2250</v>
+        <v>1690</v>
       </c>
       <c r="C4" t="n">
-        <v>4798</v>
+        <v>5774</v>
       </c>
       <c r="D4" t="n">
-        <v>2909</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1063</v>
+        <v>787</v>
       </c>
       <c r="C5" t="n">
-        <v>3544</v>
+        <v>4655</v>
       </c>
       <c r="D5" t="n">
-        <v>1360</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>285</v>
+        <v>210</v>
       </c>
       <c r="C6" t="n">
-        <v>1167</v>
+        <v>1381</v>
       </c>
       <c r="D6" t="n">
-        <v>952</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>308</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7677</v>
+        <v>1731</v>
       </c>
       <c r="C2" t="n">
-        <v>11275</v>
+        <v>9144</v>
       </c>
       <c r="D2" t="n">
-        <v>24278</v>
+        <v>20352</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3087</v>
+        <v>1716</v>
       </c>
       <c r="C3" t="n">
-        <v>4652</v>
+        <v>4964</v>
       </c>
       <c r="D3" t="n">
-        <v>9991</v>
+        <v>11207</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1579</v>
+        <v>1556</v>
       </c>
       <c r="C4" t="n">
-        <v>3898</v>
+        <v>5270</v>
       </c>
       <c r="D4" t="n">
-        <v>3242</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>859</v>
+        <v>1055</v>
       </c>
       <c r="C5" t="n">
-        <v>3022</v>
+        <v>5127</v>
       </c>
       <c r="D5" t="n">
-        <v>1274</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>317</v>
+        <v>419</v>
       </c>
       <c r="C6" t="n">
-        <v>1576</v>
+        <v>2969</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>857</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>471</v>
+        <v>813</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>616</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5405</v>
+        <v>1433</v>
       </c>
       <c r="C2" t="n">
-        <v>10143</v>
+        <v>7494</v>
       </c>
       <c r="D2" t="n">
-        <v>19561</v>
+        <v>21861</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4456</v>
+        <v>1428</v>
       </c>
       <c r="C3" t="n">
-        <v>7379</v>
+        <v>6065</v>
       </c>
       <c r="D3" t="n">
-        <v>11655</v>
+        <v>11697</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2040</v>
+        <v>1410</v>
       </c>
       <c r="C4" t="n">
-        <v>4228</v>
+        <v>5010</v>
       </c>
       <c r="D4" t="n">
-        <v>4472</v>
+        <v>4965</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1077</v>
+        <v>1128</v>
       </c>
       <c r="C5" t="n">
-        <v>3472</v>
+        <v>5038</v>
       </c>
       <c r="D5" t="n">
-        <v>1632</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>544</v>
+        <v>629</v>
       </c>
       <c r="C6" t="n">
-        <v>2375</v>
+        <v>3933</v>
       </c>
       <c r="D6" t="n">
-        <v>861</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="C7" t="n">
-        <v>1088</v>
+        <v>1776</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>647</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>356</v>
+        <v>526</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4725</v>
+        <v>1389</v>
       </c>
       <c r="C2" t="n">
-        <v>6931</v>
+        <v>4736</v>
       </c>
       <c r="D2" t="n">
-        <v>21934</v>
+        <v>17363</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4049</v>
+        <v>2174</v>
       </c>
       <c r="C3" t="n">
-        <v>7681</v>
+        <v>8860</v>
       </c>
       <c r="D3" t="n">
-        <v>12080</v>
+        <v>12784</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2743</v>
+        <v>1042</v>
       </c>
       <c r="C4" t="n">
-        <v>5894</v>
+        <v>7866</v>
       </c>
       <c r="D4" t="n">
-        <v>5715</v>
+        <v>4546</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1364</v>
+        <v>581</v>
       </c>
       <c r="C5" t="n">
-        <v>3806</v>
+        <v>3854</v>
       </c>
       <c r="D5" t="n">
-        <v>2100</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>729</v>
+        <v>210</v>
       </c>
       <c r="C6" t="n">
-        <v>2893</v>
+        <v>1740</v>
       </c>
       <c r="D6" t="n">
-        <v>973</v>
+        <v>634</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>319</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>1756</v>
+        <v>515</v>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>721</v>
+        <v>279</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
